--- a/Excel/StartConfig/Google/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Google/StartSceneConfig@s.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" activeTab="2"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="StartSceneConfig" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="50">
   <si>
     <t>Id</t>
   </si>
@@ -73,7 +73,7 @@
     <t>#20004-20100</t>
   </si>
   <si>
-    <t>#3区封测区</t>
+    <t>#171</t>
   </si>
   <si>
     <t>Account</t>
@@ -158,9 +158,6 @@
   </si>
   <si>
     <t>Happy</t>
-  </si>
-  <si>
-    <t>#171</t>
   </si>
   <si>
     <t>Center</t>
@@ -1276,10 +1273,10 @@
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="8">
-        <v>301</v>
+        <v>17101</v>
       </c>
       <c r="D7" s="3">
-        <v>3</v>
+        <v>171</v>
       </c>
       <c r="E7" s="5">
         <v>1</v>
@@ -1291,7 +1288,7 @@
         <v>15</v>
       </c>
       <c r="H7" s="3">
-        <v>20325</v>
+        <v>20575</v>
       </c>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
@@ -1303,10 +1300,10 @@
     </row>
     <row r="8" s="1" customFormat="1" spans="3:15">
       <c r="C8" s="8">
-        <v>302</v>
+        <v>17102</v>
       </c>
       <c r="D8" s="5">
-        <v>3</v>
+        <v>171</v>
       </c>
       <c r="E8" s="5">
         <v>1</v>
@@ -1317,8 +1314,8 @@
       <c r="G8" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H8" s="5">
-        <v>20326</v>
+      <c r="H8" s="3">
+        <v>20576</v>
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
@@ -1330,10 +1327,10 @@
     </row>
     <row r="9" spans="3:8">
       <c r="C9" s="8">
-        <v>303</v>
-      </c>
-      <c r="D9" s="5">
-        <v>3</v>
+        <v>17103</v>
+      </c>
+      <c r="D9" s="3">
+        <v>171</v>
       </c>
       <c r="E9" s="5">
         <v>1</v>
@@ -1345,15 +1342,15 @@
         <v>18</v>
       </c>
       <c r="H9" s="3">
-        <v>20327</v>
+        <v>20577</v>
       </c>
     </row>
     <row r="10" spans="3:8">
       <c r="C10" s="8">
-        <v>304</v>
-      </c>
-      <c r="D10" s="3">
-        <v>3</v>
+        <v>17104</v>
+      </c>
+      <c r="D10" s="5">
+        <v>171</v>
       </c>
       <c r="E10" s="3">
         <v>1</v>
@@ -1364,16 +1361,16 @@
       <c r="G10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H10" s="5">
-        <v>20328</v>
+      <c r="H10" s="3">
+        <v>20578</v>
       </c>
     </row>
     <row r="11" spans="3:7">
       <c r="C11" s="8">
-        <v>305</v>
-      </c>
-      <c r="D11" s="5">
-        <v>3</v>
+        <v>17105</v>
+      </c>
+      <c r="D11" s="3">
+        <v>171</v>
       </c>
       <c r="E11" s="5">
         <v>1</v>
@@ -1387,10 +1384,10 @@
     </row>
     <row r="12" spans="3:7">
       <c r="C12" s="8">
-        <v>306</v>
-      </c>
-      <c r="D12" s="3">
-        <v>3</v>
+        <v>17106</v>
+      </c>
+      <c r="D12" s="5">
+        <v>171</v>
       </c>
       <c r="E12" s="5">
         <v>1</v>
@@ -1404,10 +1401,10 @@
     </row>
     <row r="13" spans="3:7">
       <c r="C13" s="8">
-        <v>307</v>
-      </c>
-      <c r="D13" s="5">
-        <v>3</v>
+        <v>17107</v>
+      </c>
+      <c r="D13" s="3">
+        <v>171</v>
       </c>
       <c r="E13" s="5">
         <v>1</v>
@@ -1421,10 +1418,10 @@
     </row>
     <row r="14" spans="3:7">
       <c r="C14" s="8">
-        <v>308</v>
+        <v>17108</v>
       </c>
       <c r="D14" s="5">
-        <v>3</v>
+        <v>171</v>
       </c>
       <c r="E14" s="3">
         <v>1</v>
@@ -1438,10 +1435,10 @@
     </row>
     <row r="15" spans="3:7">
       <c r="C15" s="8">
-        <v>309</v>
+        <v>17109</v>
       </c>
       <c r="D15" s="3">
-        <v>3</v>
+        <v>171</v>
       </c>
       <c r="E15" s="5">
         <v>1</v>
@@ -1455,10 +1452,10 @@
     </row>
     <row r="16" spans="3:7">
       <c r="C16" s="8">
-        <v>310</v>
+        <v>17110</v>
       </c>
       <c r="D16" s="5">
-        <v>3</v>
+        <v>171</v>
       </c>
       <c r="E16" s="5">
         <v>1</v>
@@ -1472,10 +1469,10 @@
     </row>
     <row r="17" spans="3:7">
       <c r="C17" s="8">
-        <v>311</v>
-      </c>
-      <c r="D17" s="5">
-        <v>3</v>
+        <v>17111</v>
+      </c>
+      <c r="D17" s="3">
+        <v>171</v>
       </c>
       <c r="E17" s="5">
         <v>1</v>
@@ -1489,10 +1486,10 @@
     </row>
     <row r="18" spans="3:7">
       <c r="C18" s="8">
-        <v>312</v>
-      </c>
-      <c r="D18" s="3">
-        <v>3</v>
+        <v>17112</v>
+      </c>
+      <c r="D18" s="5">
+        <v>171</v>
       </c>
       <c r="E18" s="3">
         <v>1</v>
@@ -1506,10 +1503,10 @@
     </row>
     <row r="19" spans="3:7">
       <c r="C19" s="8">
-        <v>313</v>
-      </c>
-      <c r="D19" s="5">
-        <v>3</v>
+        <v>17113</v>
+      </c>
+      <c r="D19" s="3">
+        <v>171</v>
       </c>
       <c r="E19" s="5">
         <v>1</v>
@@ -1523,10 +1520,10 @@
     </row>
     <row r="20" spans="3:7">
       <c r="C20" s="8">
-        <v>314</v>
+        <v>17114</v>
       </c>
       <c r="D20" s="5">
-        <v>3</v>
+        <v>171</v>
       </c>
       <c r="E20" s="5">
         <v>1</v>
@@ -1540,10 +1537,10 @@
     </row>
     <row r="21" spans="3:7">
       <c r="C21" s="8">
-        <v>315</v>
+        <v>17115</v>
       </c>
       <c r="D21" s="3">
-        <v>3</v>
+        <v>171</v>
       </c>
       <c r="E21" s="5">
         <v>1</v>
@@ -1557,10 +1554,10 @@
     </row>
     <row r="22" spans="3:7">
       <c r="C22" s="8">
-        <v>316</v>
-      </c>
-      <c r="D22" s="3">
-        <v>3</v>
+        <v>17116</v>
+      </c>
+      <c r="D22" s="5">
+        <v>171</v>
       </c>
       <c r="E22" s="3">
         <v>1</v>
@@ -1574,10 +1571,10 @@
     </row>
     <row r="23" spans="3:7">
       <c r="C23" s="8">
-        <v>317</v>
-      </c>
-      <c r="D23" s="5">
-        <v>3</v>
+        <v>17117</v>
+      </c>
+      <c r="D23" s="3">
+        <v>171</v>
       </c>
       <c r="E23" s="5">
         <v>1</v>
@@ -1591,10 +1588,10 @@
     </row>
     <row r="24" spans="3:7">
       <c r="C24" s="8">
-        <v>318</v>
-      </c>
-      <c r="D24" s="3">
-        <v>3</v>
+        <v>17118</v>
+      </c>
+      <c r="D24" s="5">
+        <v>171</v>
       </c>
       <c r="E24" s="5">
         <v>1</v>
@@ -1608,10 +1605,10 @@
     </row>
     <row r="25" spans="3:7">
       <c r="C25" s="8">
-        <v>319</v>
-      </c>
-      <c r="D25" s="5">
-        <v>3</v>
+        <v>17119</v>
+      </c>
+      <c r="D25" s="3">
+        <v>171</v>
       </c>
       <c r="E25" s="5">
         <v>1</v>
@@ -1625,10 +1622,10 @@
     </row>
     <row r="26" spans="3:7">
       <c r="C26" s="8">
-        <v>320</v>
-      </c>
-      <c r="D26" s="3">
-        <v>3</v>
+        <v>17120</v>
+      </c>
+      <c r="D26" s="5">
+        <v>171</v>
       </c>
       <c r="E26" s="3">
         <v>1</v>
@@ -1642,10 +1639,10 @@
     </row>
     <row r="27" spans="3:7">
       <c r="C27" s="8">
-        <v>321</v>
+        <v>17121</v>
       </c>
       <c r="D27" s="3">
-        <v>3</v>
+        <v>171</v>
       </c>
       <c r="E27" s="5">
         <v>1</v>
@@ -1659,10 +1656,10 @@
     </row>
     <row r="28" spans="3:7">
       <c r="C28" s="8">
-        <v>322</v>
-      </c>
-      <c r="D28" s="3">
-        <v>3</v>
+        <v>17122</v>
+      </c>
+      <c r="D28" s="5">
+        <v>171</v>
       </c>
       <c r="E28" s="5">
         <v>1</v>
@@ -1676,10 +1673,10 @@
     </row>
     <row r="29" spans="3:7">
       <c r="C29" s="8">
-        <v>323</v>
+        <v>17123</v>
       </c>
       <c r="D29" s="3">
-        <v>3</v>
+        <v>171</v>
       </c>
       <c r="E29" s="5">
         <v>1</v>
@@ -1693,10 +1690,10 @@
     </row>
     <row r="30" spans="3:7">
       <c r="C30" s="8">
-        <v>324</v>
-      </c>
-      <c r="D30" s="3">
-        <v>3</v>
+        <v>17124</v>
+      </c>
+      <c r="D30" s="5">
+        <v>171</v>
       </c>
       <c r="E30" s="3">
         <v>1</v>
@@ -1710,10 +1707,10 @@
     </row>
     <row r="31" spans="3:7">
       <c r="C31" s="8">
-        <v>325</v>
+        <v>17125</v>
       </c>
       <c r="D31" s="3">
-        <v>3</v>
+        <v>171</v>
       </c>
       <c r="E31" s="5">
         <v>1</v>
@@ -1722,448 +1719,6 @@
         <v>42</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C33" s="8">
-        <v>17101</v>
-      </c>
-      <c r="D33" s="3">
-        <v>171</v>
-      </c>
-      <c r="E33" s="5">
-        <v>1</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G33" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H33" s="3">
-        <v>20575</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="8">
-        <v>17102</v>
-      </c>
-      <c r="D34" s="5">
-        <v>171</v>
-      </c>
-      <c r="E34" s="5">
-        <v>1</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G34" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H34" s="3">
-        <v>20576</v>
-      </c>
-    </row>
-    <row r="35" spans="3:8">
-      <c r="C35" s="8">
-        <v>17103</v>
-      </c>
-      <c r="D35" s="3">
-        <v>171</v>
-      </c>
-      <c r="E35" s="5">
-        <v>1</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H35" s="3">
-        <v>20577</v>
-      </c>
-    </row>
-    <row r="36" spans="3:8">
-      <c r="C36" s="8">
-        <v>17104</v>
-      </c>
-      <c r="D36" s="5">
-        <v>171</v>
-      </c>
-      <c r="E36" s="3">
-        <v>1</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H36" s="3">
-        <v>20578</v>
-      </c>
-    </row>
-    <row r="37" spans="3:7">
-      <c r="C37" s="8">
-        <v>17105</v>
-      </c>
-      <c r="D37" s="3">
-        <v>171</v>
-      </c>
-      <c r="E37" s="5">
-        <v>1</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="38" spans="3:7">
-      <c r="C38" s="8">
-        <v>17106</v>
-      </c>
-      <c r="D38" s="5">
-        <v>171</v>
-      </c>
-      <c r="E38" s="5">
-        <v>1</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="39" spans="3:7">
-      <c r="C39" s="8">
-        <v>17107</v>
-      </c>
-      <c r="D39" s="3">
-        <v>171</v>
-      </c>
-      <c r="E39" s="5">
-        <v>1</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="40" spans="3:7">
-      <c r="C40" s="8">
-        <v>17108</v>
-      </c>
-      <c r="D40" s="5">
-        <v>171</v>
-      </c>
-      <c r="E40" s="3">
-        <v>1</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="41" spans="3:7">
-      <c r="C41" s="8">
-        <v>17109</v>
-      </c>
-      <c r="D41" s="3">
-        <v>171</v>
-      </c>
-      <c r="E41" s="5">
-        <v>1</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="42" spans="3:7">
-      <c r="C42" s="8">
-        <v>17110</v>
-      </c>
-      <c r="D42" s="5">
-        <v>171</v>
-      </c>
-      <c r="E42" s="5">
-        <v>1</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="43" spans="3:7">
-      <c r="C43" s="8">
-        <v>17111</v>
-      </c>
-      <c r="D43" s="3">
-        <v>171</v>
-      </c>
-      <c r="E43" s="5">
-        <v>1</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="44" spans="3:7">
-      <c r="C44" s="8">
-        <v>17112</v>
-      </c>
-      <c r="D44" s="5">
-        <v>171</v>
-      </c>
-      <c r="E44" s="3">
-        <v>1</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="45" spans="3:7">
-      <c r="C45" s="8">
-        <v>17113</v>
-      </c>
-      <c r="D45" s="3">
-        <v>171</v>
-      </c>
-      <c r="E45" s="5">
-        <v>1</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="46" spans="3:7">
-      <c r="C46" s="8">
-        <v>17114</v>
-      </c>
-      <c r="D46" s="5">
-        <v>171</v>
-      </c>
-      <c r="E46" s="5">
-        <v>1</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="47" spans="3:7">
-      <c r="C47" s="8">
-        <v>17115</v>
-      </c>
-      <c r="D47" s="3">
-        <v>171</v>
-      </c>
-      <c r="E47" s="5">
-        <v>1</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="48" spans="3:7">
-      <c r="C48" s="8">
-        <v>17116</v>
-      </c>
-      <c r="D48" s="5">
-        <v>171</v>
-      </c>
-      <c r="E48" s="3">
-        <v>1</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="49" spans="3:7">
-      <c r="C49" s="8">
-        <v>17117</v>
-      </c>
-      <c r="D49" s="3">
-        <v>171</v>
-      </c>
-      <c r="E49" s="5">
-        <v>1</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="50" spans="3:7">
-      <c r="C50" s="8">
-        <v>17118</v>
-      </c>
-      <c r="D50" s="5">
-        <v>171</v>
-      </c>
-      <c r="E50" s="5">
-        <v>1</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="51" spans="3:7">
-      <c r="C51" s="8">
-        <v>17119</v>
-      </c>
-      <c r="D51" s="3">
-        <v>171</v>
-      </c>
-      <c r="E51" s="5">
-        <v>1</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="52" spans="3:7">
-      <c r="C52" s="8">
-        <v>17120</v>
-      </c>
-      <c r="D52" s="5">
-        <v>171</v>
-      </c>
-      <c r="E52" s="3">
-        <v>1</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="53" spans="3:7">
-      <c r="C53" s="8">
-        <v>17121</v>
-      </c>
-      <c r="D53" s="3">
-        <v>171</v>
-      </c>
-      <c r="E53" s="5">
-        <v>1</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="54" spans="3:7">
-      <c r="C54" s="8">
-        <v>17122</v>
-      </c>
-      <c r="D54" s="5">
-        <v>171</v>
-      </c>
-      <c r="E54" s="5">
-        <v>1</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="55" spans="3:7">
-      <c r="C55" s="8">
-        <v>17123</v>
-      </c>
-      <c r="D55" s="3">
-        <v>171</v>
-      </c>
-      <c r="E55" s="5">
-        <v>1</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="56" spans="3:7">
-      <c r="C56" s="8">
-        <v>17124</v>
-      </c>
-      <c r="D56" s="5">
-        <v>171</v>
-      </c>
-      <c r="E56" s="3">
-        <v>1</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G56" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="57" spans="3:7">
-      <c r="C57" s="8">
-        <v>17125</v>
-      </c>
-      <c r="D57" s="3">
-        <v>171</v>
-      </c>
-      <c r="E57" s="5">
-        <v>1</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G57" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -2285,10 +1840,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -2303,10 +1858,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -2321,10 +1876,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -2339,10 +1894,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -2359,10 +1914,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -2457,10 +2012,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="G6" s="5" t="s">
         <v>49</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>50</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Google/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Google/StartSceneConfig@s.xlsx
@@ -73,7 +73,7 @@
     <t>#20004-20100</t>
   </si>
   <si>
-    <t>#171</t>
+    <t>#171ValorArena</t>
   </si>
   <si>
     <t>Account</t>
